--- a/03_Consumo_Energia_limpio.xlsx
+++ b/03_Consumo_Energia_limpio.xlsx
@@ -1049,16 +1049,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nulos</t>
+          <t>Tipos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>'temperatura' imputados con la mediana (22.4)</t>
+          <t>'fecha' convertida a datetime</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'humedad' imputados con la mediana (50.0)</t>
+          <t>'temperatura' rellenos con la mediana (22.4)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'equipos_activos' imputados con la mediana (28.5)</t>
+          <t>'humedad' rellenos con la mediana (50.0)</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1094,12 +1094,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Outliers</t>
+          <t>Nulos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>'temperatura' recortados a [15.4, 29.0] (antes=[500.0], después=[28.999999999999996])</t>
+          <t>'equipos_activos' rellenos con la mediana (28.5)</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'humedad' recortados a [44.5, 56.5] (antes=[57.0], después=[56.5])</t>
+          <t>'temperatura' recortados a [15.4, 29.0] (antes=[500.0], después=[28.999999999999996])</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1129,11 +1129,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>'personas' recortados a [47.5, 107.5] (antes=[42.0, 40.0], después=[47.5, 47.5])</t>
+          <t>'humedad' recortados a [44.5, 56.5] (antes=[57.0], después=[56.5])</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1144,43 +1144,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>'consumo_kwh' recortados a [44.5, 224.2] (antes=[9999.0], después=[224.15000000000003])</t>
+          <t>'personas' recortados a [47.5, 107.5] (antes=[42.0, 40.0], después=[47.5, 47.5])</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Filas</t>
+          <t>Outliers</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>total: originales -&gt; limpias</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>14 -&gt; 13</t>
-        </is>
+          <t>'consumo_kwh' recortados a [44.5, 224.2] (antes=[9999.0], después=[224.15000000000003])</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tipos</t>
+          <t>Filas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>'fecha' convertida a fecha (datetime)</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>13</v>
+          <t>total: originales -&gt; limpias</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14 -&gt; 13</t>
+        </is>
       </c>
     </row>
   </sheetData>
